--- a/students dashboard/img/Excel Database/NCbaEnrollment_G9.xlsx
+++ b/students dashboard/img/Excel Database/NCbaEnrollment_G9.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6880"/>
+    <workbookView windowWidth="19190" windowHeight="6800"/>
   </bookViews>
   <sheets>
     <sheet name="NCbaEnrollment_List_school" sheetId="1" r:id="rId1"/>
